--- a/products.xlsx
+++ b/products.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1219">
   <si>
     <t>id</t>
   </si>
@@ -3400,6 +3400,276 @@
     <t>zalimlotion.jpg</t>
   </si>
   <si>
+    <t>Excel se Website update - Kaise use karein</t>
+  </si>
+  <si>
+    <t>1. 'Products' sheet me MRP, discount, scheme, stock (inStock) edit karo.</t>
+  </si>
+  <si>
+    <t>2. Naya product: sabse neeche nayi row me likho. 'id' khali chhodo to automatically agla number mil jayega.</t>
+  </si>
+  <si>
+    <t>3. bestseller / inStock: dropdown se TRUE ya FALSE chuno. Stock khatam = inStock FALSE.</t>
+  </si>
+  <si>
+    <t>4. discount / scheme: nahi hai to khali chhodo. Likh sakte ho jaise 10 ya '10+1 free'.</t>
+  </si>
+  <si>
+    <t>5. image: sirf file ka naam likho (jaise acnetoin_soap.jpg). Ek se zyada photo ho to comma se alag karo: a.jpg, b.jpg</t>
+  </si>
+  <si>
+    <t>6. Photos GitHub ke 'images' folder me upload karni hain (naam bilkul wahi jo Excel me likha hai).</t>
+  </si>
+  <si>
+    <t>7. Product hatana ho to puri row delete karo.</t>
+  </si>
+  <si>
+    <t>8. products.xlsx ko GitHub repo me replace upload karo. 1-2 minute me website update ho jayegi.</t>
+  </si>
+  <si>
+    <t>Dhyan: Row 1 ke header ka naam mat badlo. Price sirf number me likho. File ka naam products.xlsx hi rakho.</t>
+  </si>
+  <si>
+    <t>earwell_drop.jpg, earwell_drop_box.jpg</t>
+  </si>
+  <si>
+    <t>Chlorhexidine Gluconate + Clobetasol + Miconazole + Neomycin</t>
+  </si>
+  <si>
+    <t>Paracetamol + Mefenamic</t>
+  </si>
+  <si>
+    <t>Ofloxacin + Metronidazole</t>
+  </si>
+  <si>
+    <t>Antifungal nail, skin, oral, systemic fungal infections</t>
+  </si>
+  <si>
+    <t>Antibiotic ear/throat/UTI/respiratory bacterial infections</t>
+  </si>
+  <si>
+    <t>KETOROL DT TAB</t>
+  </si>
+  <si>
+    <t>15*15</t>
+  </si>
+  <si>
+    <t>Dental pain, dant dard, daant ka dard, toothache, moderate to severe pain, tez dard, post-operative pain, operation ke baad dard, sujan</t>
+  </si>
+  <si>
+    <t>ketorol_dt_tab.jpg</t>
+  </si>
+  <si>
+    <t>MAHACEF 200 TAB</t>
+  </si>
+  <si>
+    <t>Bacterial infection, typhoid, UTI, peshab ka infection, throat infection, gale ka infection, ear infection, kaan ka infection, bukhar, respiratory infection</t>
+  </si>
+  <si>
+    <t>mahacef_200_tab.jpg</t>
+  </si>
+  <si>
+    <t>TELVAS 40 TAB</t>
+  </si>
+  <si>
+    <t>Telmisartan 40mg</t>
+  </si>
+  <si>
+    <t>High blood pressure, high BP, hypertension, BP ki dawai, heart protection, dil ki suraksha</t>
+  </si>
+  <si>
+    <t>telvas_40_tab.jpg</t>
+  </si>
+  <si>
+    <t>P40 TAB</t>
+  </si>
+  <si>
+    <t>Acidity, gas, GERD, seene mein jalan, heartburn, pet mein jalan, stomach ulcer, pet ka alsar, acid reflux</t>
+  </si>
+  <si>
+    <t>p40_tab.jpg</t>
+  </si>
+  <si>
+    <t>RABITOP DSR CAP</t>
+  </si>
+  <si>
+    <t>Rabeprazole 20mg + Domperidone 30mg (SR)</t>
+  </si>
+  <si>
+    <t>Acidity, gas, GERD, seene mein jalan, ulti, nausea, ji machlana, pet fulna, bloating, indigestion, ajeerna</t>
+  </si>
+  <si>
+    <t>rabitop_dsr_tab.jpg</t>
+  </si>
+  <si>
+    <t>MAHAMOX CV 625 TAB</t>
+  </si>
+  <si>
+    <t>Amoxicillin 500mg + Clavulanic Acid 125mg</t>
+  </si>
+  <si>
+    <t>Bacterial infection, throat infection, gale ka infection, chest infection, sinus, UTI, peshab infection, skin infection, tooth infection, dant ka infection</t>
+  </si>
+  <si>
+    <t>mahamox_cv_625_tab.jpg</t>
+  </si>
+  <si>
+    <t>FASTAC Fast Action tab</t>
+  </si>
+  <si>
+    <t>1*15</t>
+  </si>
+  <si>
+    <t>painkiller +anti-inflammatory + fever + bodypain + dard</t>
+  </si>
+  <si>
+    <t>fastac_fast_action_tab.jpg</t>
+  </si>
+  <si>
+    <t>ORASORE DENTAL GEL</t>
+  </si>
+  <si>
+    <t>WINGS PHARMA</t>
+  </si>
+  <si>
+    <t>6*10G</t>
+  </si>
+  <si>
+    <t>Benzocaine</t>
+  </si>
+  <si>
+    <t>Dental pain, dant dard, mouth ulcer, munh ke chhale, gum pain, masoodon ka dard, teething pain, dant nikalne ka dard</t>
+  </si>
+  <si>
+    <t>orasore_dental_gel.jpg</t>
+  </si>
+  <si>
+    <t>LEEZOLE 3 KIT TAB</t>
+  </si>
+  <si>
+    <t>1 Kit</t>
+  </si>
+  <si>
+    <t>Fluconazole 150mg + Azithromycin 1g + Secnidazole 1g</t>
+  </si>
+  <si>
+    <t>Vaginal infection, white discharge, safed pani, fungal infection, STI, bacterial vaginosis, yeast infection</t>
+  </si>
+  <si>
+    <t>leezole_3_kit.jpg</t>
+  </si>
+  <si>
+    <t>PREGABANYL M CAP</t>
+  </si>
+  <si>
+    <t>Pregabalin 75mg + Methylcobalamin 750mcg</t>
+  </si>
+  <si>
+    <t>Nerve pain, neuropathic pain, nason ka dard, jhunjhuni, numbness, sunn hona, diabetic neuropathy, sciatica, vitamin B12 deficiency</t>
+  </si>
+  <si>
+    <t>pregabanyl_m_cap.jpg</t>
+  </si>
+  <si>
+    <t>RECOPRESS 500 TAB</t>
+  </si>
+  <si>
+    <t>10*1*6</t>
+  </si>
+  <si>
+    <t>disulfiram 500mg</t>
+  </si>
+  <si>
+    <t>recopress_500_tab.jpg</t>
+  </si>
+  <si>
+    <t>PET SAFA GRANULES</t>
+  </si>
+  <si>
+    <t>60G</t>
+  </si>
+  <si>
+    <t>Ayurvedic herbal blend</t>
+  </si>
+  <si>
+    <t>Kabz, constipation, pet saaf, pet safa, gas, acidity, digestion, pachan</t>
+  </si>
+  <si>
+    <t>petsaffa_60g.jpg</t>
+  </si>
+  <si>
+    <t>TRIPHALA CHURNA</t>
+  </si>
+  <si>
+    <t>BAIDYANATH</t>
+  </si>
+  <si>
+    <t>50G</t>
+  </si>
+  <si>
+    <t>Haritaki, Bibhitaki, Amalaki (Amla)</t>
+  </si>
+  <si>
+    <t>Kabz, constipation, digestion, pachan, detox, weight loss, eye health, aankhon ke liye, immunity</t>
+  </si>
+  <si>
+    <t>triphala.jpg</t>
+  </si>
+  <si>
+    <t>MAHANARAYAN OIL B</t>
+  </si>
+  <si>
+    <t>Ayurvedic oil (Bilva, Agnimantha, Ashwagandha etc. in Til oil)</t>
+  </si>
+  <si>
+    <t>Joint pain, jodon ka dard, arthritis, gathiya, muscle pain, maans-peshiyon ka dard, kamar dard, back pain, malish, body massage</t>
+  </si>
+  <si>
+    <t>mahanarayan_tel_b.jpg</t>
+  </si>
+  <si>
+    <t>KAYAM CHURNA</t>
+  </si>
+  <si>
+    <t>Senna (Sanay), Haritaki, Saunf, Sonth etc. (Ayurvedic)</t>
+  </si>
+  <si>
+    <t>Kabz, constipation, pet saaf, gas, pachan, ajeerna, bloating</t>
+  </si>
+  <si>
+    <t>kayam_churna_50g.jpg</t>
+  </si>
+  <si>
+    <t>LACTOBIOTIC RESPULE</t>
+  </si>
+  <si>
+    <t>LUPIN</t>
+  </si>
+  <si>
+    <t>10*5*5ML</t>
+  </si>
+  <si>
+    <t>Bacillus Clausii Spores</t>
+  </si>
+  <si>
+    <t>Diarrhea (Dast / Loose Motions) + Pet phoolna (bloating), gas</t>
+  </si>
+  <si>
+    <t>lactobiotic_spores.jpg</t>
+  </si>
+  <si>
+    <t>treat chronic alcohol addiction</t>
+  </si>
+  <si>
+    <t>CHARMOJA OINT 15G</t>
+  </si>
+  <si>
+    <t>Ringworm + Itching + Khujli + Eczema + Anti-bacterial and antifungal infections</t>
+  </si>
+  <si>
+    <t>charmoja.jpg</t>
+  </si>
+  <si>
     <t>L HIST MONT SYP</t>
   </si>
   <si>
@@ -3410,267 +3680,6 @@
   </si>
   <si>
     <t>l_hist_mont_syp.jpg</t>
-  </si>
-  <si>
-    <t>Excel se Website update - Kaise use karein</t>
-  </si>
-  <si>
-    <t>1. 'Products' sheet me MRP, discount, scheme, stock (inStock) edit karo.</t>
-  </si>
-  <si>
-    <t>2. Naya product: sabse neeche nayi row me likho. 'id' khali chhodo to automatically agla number mil jayega.</t>
-  </si>
-  <si>
-    <t>3. bestseller / inStock: dropdown se TRUE ya FALSE chuno. Stock khatam = inStock FALSE.</t>
-  </si>
-  <si>
-    <t>4. discount / scheme: nahi hai to khali chhodo. Likh sakte ho jaise 10 ya '10+1 free'.</t>
-  </si>
-  <si>
-    <t>5. image: sirf file ka naam likho (jaise acnetoin_soap.jpg). Ek se zyada photo ho to comma se alag karo: a.jpg, b.jpg</t>
-  </si>
-  <si>
-    <t>6. Photos GitHub ke 'images' folder me upload karni hain (naam bilkul wahi jo Excel me likha hai).</t>
-  </si>
-  <si>
-    <t>7. Product hatana ho to puri row delete karo.</t>
-  </si>
-  <si>
-    <t>8. products.xlsx ko GitHub repo me replace upload karo. 1-2 minute me website update ho jayegi.</t>
-  </si>
-  <si>
-    <t>Dhyan: Row 1 ke header ka naam mat badlo. Price sirf number me likho. File ka naam products.xlsx hi rakho.</t>
-  </si>
-  <si>
-    <t>earwell_drop.jpg, earwell_drop_box.jpg</t>
-  </si>
-  <si>
-    <t>Chlorhexidine Gluconate + Clobetasol + Miconazole + Neomycin</t>
-  </si>
-  <si>
-    <t>Paracetamol + Mefenamic</t>
-  </si>
-  <si>
-    <t>Ofloxacin + Metronidazole</t>
-  </si>
-  <si>
-    <t>Antifungal nail, skin, oral, systemic fungal infections</t>
-  </si>
-  <si>
-    <t>Antibiotic ear/throat/UTI/respiratory bacterial infections</t>
-  </si>
-  <si>
-    <t>KETOROL DT TAB</t>
-  </si>
-  <si>
-    <t>15*15</t>
-  </si>
-  <si>
-    <t>Dental pain, dant dard, daant ka dard, toothache, moderate to severe pain, tez dard, post-operative pain, operation ke baad dard, sujan</t>
-  </si>
-  <si>
-    <t>ketorol_dt_tab.jpg</t>
-  </si>
-  <si>
-    <t>MAHACEF 200 TAB</t>
-  </si>
-  <si>
-    <t>Bacterial infection, typhoid, UTI, peshab ka infection, throat infection, gale ka infection, ear infection, kaan ka infection, bukhar, respiratory infection</t>
-  </si>
-  <si>
-    <t>mahacef_200_tab.jpg</t>
-  </si>
-  <si>
-    <t>TELVAS 40 TAB</t>
-  </si>
-  <si>
-    <t>Telmisartan 40mg</t>
-  </si>
-  <si>
-    <t>High blood pressure, high BP, hypertension, BP ki dawai, heart protection, dil ki suraksha</t>
-  </si>
-  <si>
-    <t>telvas_40_tab.jpg</t>
-  </si>
-  <si>
-    <t>P40 TAB</t>
-  </si>
-  <si>
-    <t>Acidity, gas, GERD, seene mein jalan, heartburn, pet mein jalan, stomach ulcer, pet ka alsar, acid reflux</t>
-  </si>
-  <si>
-    <t>p40_tab.jpg</t>
-  </si>
-  <si>
-    <t>RABITOP DSR CAP</t>
-  </si>
-  <si>
-    <t>Rabeprazole 20mg + Domperidone 30mg (SR)</t>
-  </si>
-  <si>
-    <t>Acidity, gas, GERD, seene mein jalan, ulti, nausea, ji machlana, pet fulna, bloating, indigestion, ajeerna</t>
-  </si>
-  <si>
-    <t>rabitop_dsr_tab.jpg</t>
-  </si>
-  <si>
-    <t>MAHAMOX CV 625 TAB</t>
-  </si>
-  <si>
-    <t>Amoxicillin 500mg + Clavulanic Acid 125mg</t>
-  </si>
-  <si>
-    <t>Bacterial infection, throat infection, gale ka infection, chest infection, sinus, UTI, peshab infection, skin infection, tooth infection, dant ka infection</t>
-  </si>
-  <si>
-    <t>mahamox_cv_625_tab.jpg</t>
-  </si>
-  <si>
-    <t>FASTAC Fast Action tab</t>
-  </si>
-  <si>
-    <t>1*15</t>
-  </si>
-  <si>
-    <t>painkiller +anti-inflammatory + fever + bodypain + dard</t>
-  </si>
-  <si>
-    <t>fastac_fast_action_tab.jpg</t>
-  </si>
-  <si>
-    <t>ORASORE DENTAL GEL</t>
-  </si>
-  <si>
-    <t>WINGS PHARMA</t>
-  </si>
-  <si>
-    <t>6*10G</t>
-  </si>
-  <si>
-    <t>Benzocaine</t>
-  </si>
-  <si>
-    <t>Dental pain, dant dard, mouth ulcer, munh ke chhale, gum pain, masoodon ka dard, teething pain, dant nikalne ka dard</t>
-  </si>
-  <si>
-    <t>orasore_dental_gel.jpg</t>
-  </si>
-  <si>
-    <t>LEEZOLE 3 KIT TAB</t>
-  </si>
-  <si>
-    <t>1 Kit</t>
-  </si>
-  <si>
-    <t>Fluconazole 150mg + Azithromycin 1g + Secnidazole 1g</t>
-  </si>
-  <si>
-    <t>Vaginal infection, white discharge, safed pani, fungal infection, STI, bacterial vaginosis, yeast infection</t>
-  </si>
-  <si>
-    <t>leezole_3_kit.jpg</t>
-  </si>
-  <si>
-    <t>PREGABANYL M CAP</t>
-  </si>
-  <si>
-    <t>Pregabalin 75mg + Methylcobalamin 750mcg</t>
-  </si>
-  <si>
-    <t>Nerve pain, neuropathic pain, nason ka dard, jhunjhuni, numbness, sunn hona, diabetic neuropathy, sciatica, vitamin B12 deficiency</t>
-  </si>
-  <si>
-    <t>pregabanyl_m_cap.jpg</t>
-  </si>
-  <si>
-    <t>RECOPRESS 500 TAB</t>
-  </si>
-  <si>
-    <t>10*1*6</t>
-  </si>
-  <si>
-    <t>disulfiram 500mg</t>
-  </si>
-  <si>
-    <t>Verify karke likhein</t>
-  </si>
-  <si>
-    <t>recopress_500_tab.jpg</t>
-  </si>
-  <si>
-    <t>PET SAFA GRANULES</t>
-  </si>
-  <si>
-    <t>60G</t>
-  </si>
-  <si>
-    <t>Ayurvedic herbal blend</t>
-  </si>
-  <si>
-    <t>Kabz, constipation, pet saaf, pet safa, gas, acidity, digestion, pachan</t>
-  </si>
-  <si>
-    <t>petsaffa_60g.jpg</t>
-  </si>
-  <si>
-    <t>TRIPHALA CHURNA</t>
-  </si>
-  <si>
-    <t>BAIDYANATH</t>
-  </si>
-  <si>
-    <t>50G</t>
-  </si>
-  <si>
-    <t>Haritaki, Bibhitaki, Amalaki (Amla)</t>
-  </si>
-  <si>
-    <t>Kabz, constipation, digestion, pachan, detox, weight loss, eye health, aankhon ke liye, immunity</t>
-  </si>
-  <si>
-    <t>triphala.jpg</t>
-  </si>
-  <si>
-    <t>MAHANARAYAN OIL B</t>
-  </si>
-  <si>
-    <t>Ayurvedic oil (Bilva, Agnimantha, Ashwagandha etc. in Til oil)</t>
-  </si>
-  <si>
-    <t>Joint pain, jodon ka dard, arthritis, gathiya, muscle pain, maans-peshiyon ka dard, kamar dard, back pain, malish, body massage</t>
-  </si>
-  <si>
-    <t>mahanarayan_tel_b.jpg</t>
-  </si>
-  <si>
-    <t>KAYAM CHURNA</t>
-  </si>
-  <si>
-    <t>Senna (Sanay), Haritaki, Saunf, Sonth etc. (Ayurvedic)</t>
-  </si>
-  <si>
-    <t>Kabz, constipation, pet saaf, gas, pachan, ajeerna, bloating</t>
-  </si>
-  <si>
-    <t>kayam_churna_50g.jpg</t>
-  </si>
-  <si>
-    <t>LACTOBIOTIC RESPULE</t>
-  </si>
-  <si>
-    <t>LUPIN</t>
-  </si>
-  <si>
-    <t>10*5*5ML</t>
-  </si>
-  <si>
-    <t>Bacillus Clausii Spores</t>
-  </si>
-  <si>
-    <t>Diarrhea (Dast / Loose Motions) + Pet phoolna (bloating), gas</t>
-  </si>
-  <si>
-    <t>lactobiotic_spores.jpg</t>
   </si>
 </sst>
 </file>
@@ -3744,7 +3753,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3842,11 +3851,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3907,8 +3946,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4212,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M300"/>
+  <dimension ref="A1:Z300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -6334,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -6931,7 +6982,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="10" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -7509,7 +7560,7 @@
         <v>235</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>326</v>
@@ -7546,7 +7597,7 @@
         <v>425</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>326</v>
@@ -9248,7 +9299,7 @@
         <v>191</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="H136" s="7" t="s">
         <v>621</v>
@@ -9507,7 +9558,7 @@
         <v>191</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="H143" s="7" t="s">
         <v>645</v>
@@ -13023,7 +13074,7 @@
         <v>1023</v>
       </c>
       <c r="H238" s="7" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="I238" s="9" t="b">
         <v>0</v>
@@ -13097,7 +13148,7 @@
         <v>1031</v>
       </c>
       <c r="H240" s="7" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="I240" s="9" t="b">
         <v>0</v>
@@ -13819,7 +13870,7 @@
         <v>336</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="C260" s="13" t="s">
         <v>170</v>
@@ -13831,13 +13882,13 @@
         <v>22</v>
       </c>
       <c r="F260" s="7" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="G260" s="14" t="s">
         <v>465</v>
       </c>
       <c r="H260" s="15" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="I260" s="9" t="b">
         <v>1</v>
@@ -13848,7 +13899,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="261" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13856,7 +13907,7 @@
         <v>248</v>
       </c>
       <c r="B261" s="16" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>541</v>
@@ -13874,7 +13925,7 @@
         <v>821</v>
       </c>
       <c r="H261" s="15" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="I261" s="9" t="b">
         <v>1</v>
@@ -13885,7 +13936,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -13893,7 +13944,7 @@
         <v>246</v>
       </c>
       <c r="B262" s="16" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="C262" s="7" t="s">
         <v>72</v>
@@ -13908,10 +13959,10 @@
         <v>93</v>
       </c>
       <c r="G262" s="14" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="H262" s="15" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="I262" s="9" t="b">
         <v>1</v>
@@ -13922,7 +13973,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -13930,7 +13981,7 @@
         <v>356</v>
       </c>
       <c r="B263" s="16" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C263" s="7" t="s">
         <v>40</v>
@@ -13948,7 +13999,7 @@
         <v>711</v>
       </c>
       <c r="H263" s="15" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="I263" s="9" t="b">
         <v>1</v>
@@ -13959,7 +14010,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -13967,7 +14018,7 @@
         <v>395</v>
       </c>
       <c r="B264" s="16" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>72</v>
@@ -13982,10 +14033,10 @@
         <v>35</v>
       </c>
       <c r="G264" s="14" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="H264" s="15" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="I264" s="9" t="b">
         <v>1</v>
@@ -13996,7 +14047,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14004,7 +14055,7 @@
         <v>394</v>
       </c>
       <c r="B265" s="16" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>541</v>
@@ -14019,10 +14070,10 @@
         <v>29</v>
       </c>
       <c r="G265" s="17" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="H265" s="15" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="I265" s="9" t="b">
         <v>1</v>
@@ -14033,7 +14084,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14041,7 +14092,7 @@
         <v>267</v>
       </c>
       <c r="B266" s="16" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>296</v>
@@ -14053,13 +14104,13 @@
         <v>22</v>
       </c>
       <c r="F266" s="7" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="G266" s="7" t="s">
         <v>349</v>
       </c>
       <c r="H266" s="15" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="I266" s="9" t="b">
         <v>1</v>
@@ -14070,7 +14121,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="267" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -14078,10 +14129,10 @@
         <v>335</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C267" s="16" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D267" s="8">
         <v>67.5</v>
@@ -14090,13 +14141,13 @@
         <v>134</v>
       </c>
       <c r="F267" s="7" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="G267" s="7" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="H267" s="15" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="I267" s="9" t="b">
         <v>1</v>
@@ -14107,7 +14158,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="18" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -14115,7 +14166,7 @@
         <v>380</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="C268" s="16" t="s">
         <v>14</v>
@@ -14127,13 +14178,13 @@
         <v>22</v>
       </c>
       <c r="F268" s="7" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="G268" s="14" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="H268" s="15" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I268" s="9" t="b">
         <v>1</v>
@@ -14144,7 +14195,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="19" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14152,7 +14203,7 @@
         <v>390</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="C269" s="16" t="s">
         <v>14</v>
@@ -14167,10 +14218,10 @@
         <v>29</v>
       </c>
       <c r="G269" s="14" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="H269" s="15" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="I269" s="9" t="b">
         <v>1</v>
@@ -14181,7 +14232,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14189,7 +14240,7 @@
         <v>391</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="C270" s="13" t="s">
         <v>14</v>
@@ -14201,13 +14252,13 @@
         <v>22</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="G270" s="14" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="H270" s="15" t="s">
-        <v>1189</v>
+        <v>1211</v>
       </c>
       <c r="I270" s="9" t="b">
         <v>1</v>
@@ -14218,7 +14269,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -14226,7 +14277,7 @@
         <v>324</v>
       </c>
       <c r="B271" s="16" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>929</v>
@@ -14238,13 +14289,13 @@
         <v>15</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="G271" s="14" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="H271" s="15" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="I271" s="9" t="b">
         <v>0</v>
@@ -14255,7 +14306,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="272" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -14263,10 +14314,10 @@
         <v>323</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="C272" s="16" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D272" s="8">
         <v>55</v>
@@ -14275,13 +14326,13 @@
         <v>15</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="G272" s="14" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="H272" s="15" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="I272" s="9" t="b">
         <v>0</v>
@@ -14292,18 +14343,18 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c r="M272" s="7" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="273" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="273" spans="1:26" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="11">
         <v>177</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="C273" s="16" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D273" s="8">
         <v>105</v>
@@ -14315,10 +14366,10 @@
         <v>1078</v>
       </c>
       <c r="G273" s="14" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="H273" s="15" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="I273" s="9" t="b">
         <v>1</v>
@@ -14329,18 +14380,18 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="274" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="274" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="11">
         <v>325</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="C274" s="13" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D274" s="8">
         <v>63</v>
@@ -14349,13 +14400,13 @@
         <v>15</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="G274" s="14" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="H274" s="15" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="I274" s="9" t="b">
         <v>0</v>
@@ -14366,18 +14417,18 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="20" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="275" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="21">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="275" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="11">
         <v>393</v>
       </c>
-      <c r="B275" s="13" t="s">
-        <v>1210</v>
+      <c r="B275" s="16" t="s">
+        <v>1205</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="D275" s="8">
         <v>77.3</v>
@@ -14386,13 +14437,13 @@
         <v>15</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>1212</v>
-      </c>
-      <c r="G275" s="17" t="s">
-        <v>1213</v>
-      </c>
-      <c r="H275" s="22" t="s">
-        <v>1214</v>
+        <v>1207</v>
+      </c>
+      <c r="G275" s="14" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H275" s="15" t="s">
+        <v>1209</v>
       </c>
       <c r="I275" s="9" t="b">
         <v>1</v>
@@ -14403,36 +14454,32 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="276" spans="1:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="6">
-        <v>1008</v>
-      </c>
-      <c r="B276" s="7" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C276" s="7" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="276" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="21">
+        <v>328</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C276" s="7"/>
+      <c r="D276" s="8">
         <v>40</v>
       </c>
-      <c r="D276" s="8">
-        <v>75</v>
-      </c>
       <c r="E276" s="7" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G276" s="7" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H276" s="7" t="s">
-        <v>1127</v>
+        <v>1007</v>
+      </c>
+      <c r="G276" s="22"/>
+      <c r="H276" s="10" t="s">
+        <v>1213</v>
       </c>
       <c r="I276" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="9" t="b">
         <v>1</v>
@@ -14440,25 +14487,60 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c r="M276" s="7" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-      <c r="G277" s="2"/>
-      <c r="H277" s="2"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="2"/>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="277" spans="1:26" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="23">
+        <v>1008</v>
+      </c>
+      <c r="B277" s="24" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C277" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D277" s="25">
+        <v>75</v>
+      </c>
+      <c r="E277" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F277" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G277" s="24" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H277" s="24" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I277" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J277" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K277" s="24"/>
+      <c r="L277" s="24"/>
+      <c r="M277" s="24" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N277" s="14"/>
+      <c r="O277" s="14"/>
+      <c r="P277" s="14"/>
+      <c r="Q277" s="14"/>
+      <c r="R277" s="14"/>
+      <c r="S277" s="14"/>
+      <c r="T277" s="14"/>
+      <c r="U277" s="14"/>
+      <c r="V277" s="14"/>
+      <c r="W277" s="14"/>
+      <c r="X277" s="14"/>
+      <c r="Y277" s="14"/>
+      <c r="Z277" s="14"/>
+    </row>
+    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -14473,7 +14555,7 @@
       <c r="L278" s="1"/>
       <c r="M278" s="2"/>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -14488,7 +14570,7 @@
       <c r="L279" s="1"/>
       <c r="M279" s="2"/>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -14503,7 +14585,7 @@
       <c r="L280" s="1"/>
       <c r="M280" s="2"/>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -14518,7 +14600,7 @@
       <c r="L281" s="1"/>
       <c r="M281" s="2"/>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -14533,7 +14615,7 @@
       <c r="L282" s="1"/>
       <c r="M282" s="2"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -14548,7 +14630,7 @@
       <c r="L283" s="1"/>
       <c r="M283" s="2"/>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -14563,7 +14645,7 @@
       <c r="L284" s="1"/>
       <c r="M284" s="2"/>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -14578,7 +14660,7 @@
       <c r="L285" s="1"/>
       <c r="M285" s="2"/>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -14593,7 +14675,7 @@
       <c r="L286" s="1"/>
       <c r="M286" s="2"/>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14608,7 +14690,7 @@
       <c r="L287" s="1"/>
       <c r="M287" s="2"/>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -14806,13 +14888,13 @@
   </sheetData>
   <autoFilter ref="A1:M2000"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="I277:J2000">
+    <dataValidation type="list" allowBlank="1" sqref="I278:J2000">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Nayi category?" error="Ye category list me nahi hai. Pakka sahi hai?" sqref="E277:E2000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Nayi category?" error="Ye category list me nahi hai. Pakka sahi hai?" sqref="E278:E2000">
       <formula1>"OTHERS,TABLET_CAP,DROP,LIQUID,CREAM_OINT"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Galat price" error="Price number hona chahiye" sqref="D277:D2000">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Galat price" error="Price number hona chahiye" sqref="D278:D2000">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -14831,7 +14913,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -14839,42 +14921,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -14882,7 +14964,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N!tE$H\Desktop\website\deepakmedical-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N!tE$H\Desktop\website\new detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1221">
   <si>
     <t>id</t>
   </si>
@@ -3680,6 +3680,12 @@
   </si>
   <si>
     <t>l_hist_mont_syp.jpg</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Rx</t>
   </si>
 </sst>
 </file>
@@ -3753,7 +3759,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3881,11 +3887,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3960,6 +3977,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4278,9 +4298,10 @@
     <col min="10" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4320,8 +4341,14 @@
       <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="27" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O1" s="27" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>98</v>
       </c>
@@ -4358,7 +4385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>58</v>
       </c>
@@ -4395,7 +4422,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>114</v>
       </c>
@@ -4432,7 +4459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>245</v>
       </c>
@@ -4469,7 +4496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>130</v>
       </c>
@@ -4506,7 +4533,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>149</v>
       </c>
@@ -4543,7 +4570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>111</v>
       </c>
@@ -4580,7 +4607,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>140</v>
       </c>
@@ -4617,7 +4644,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>105</v>
       </c>
@@ -4654,7 +4681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>150</v>
       </c>
@@ -4691,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>51</v>
       </c>
@@ -4728,7 +4755,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>52</v>
       </c>
@@ -4765,7 +4792,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>151</v>
       </c>
@@ -4802,7 +4829,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>80</v>
       </c>
@@ -4839,7 +4866,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>47</v>
       </c>
